--- a/a2_timeline.xlsx
+++ b/a2_timeline.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longh\Desktop\X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054EA544-B513-4194-BCA1-F8255AA9610B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C5A277-26B1-48E3-9352-919A2A1868BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1872" yWindow="816" windowWidth="28848" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1092" windowWidth="21480" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="macro" sheetId="1" r:id="rId1"/>
     <sheet name="Auto" sheetId="2" r:id="rId2"/>
+    <sheet name="Small-Mid-Cap" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -68,7 +69,7 @@
     <author>longh</author>
   </authors>
   <commentList>
-    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{60CF6652-2937-44A7-9D52-682AFEC1B4BE}">
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{60CF6652-2937-44A7-9D52-682AFEC1B4BE}">
       <text>
         <r>
           <rPr>
@@ -94,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{282219F5-EC72-4014-B846-51AB8DBC7857}">
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{282219F5-EC72-4014-B846-51AB8DBC7857}">
       <text>
         <r>
           <rPr>
@@ -118,7 +119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{2A3CE22C-DC57-467B-B177-4DBE1E7A1B25}">
+    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{2A3CE22C-DC57-467B-B177-4DBE1E7A1B25}">
       <text>
         <r>
           <rPr>
@@ -142,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C20" authorId="0" shapeId="0" xr:uid="{C1BC774F-FF3C-4921-AFB0-2220B7C01F82}">
+    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{C1BC774F-FF3C-4921-AFB0-2220B7C01F82}">
       <text>
         <r>
           <rPr>
@@ -171,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="222">
   <si>
     <t>Real GDP and its components</t>
   </si>
@@ -221,9 +222,6 @@
     <t>https://fred.stlouisfed.org/graph/?g=1CF1L</t>
   </si>
   <si>
-    <t>https://fred.stlouisfed.org/graph/?g=1iTKv</t>
-  </si>
-  <si>
     <t>https://fred.stlouisfed.org/graph/?g=1CEzk</t>
   </si>
   <si>
@@ -651,6 +649,218 @@
   </si>
   <si>
     <t>Consumer Situations</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/graph/?g=1JuSH</t>
+  </si>
+  <si>
+    <t>Factor</t>
+  </si>
+  <si>
+    <t>Rationale</t>
+  </si>
+  <si>
+    <t>Key Indicators</t>
+  </si>
+  <si>
+    <t>Interest Rates</t>
+  </si>
+  <si>
+    <t>Fed Funds Rate, 2Y/10Y Treasury Yield</t>
+  </si>
+  <si>
+    <t>Credit Conditions &amp; Lending Standards</t>
+  </si>
+  <si>
+    <t>SMIDs rely on bank loans/private credit; tighter standards reduce access to funding.</t>
+  </si>
+  <si>
+    <t>SLOOS, High Yield Credit Spreads</t>
+  </si>
+  <si>
+    <t>Liquidity Environment / Financial Conditions</t>
+  </si>
+  <si>
+    <t>Loose financial conditions encourage risk-taking in SMID and IPO names.</t>
+  </si>
+  <si>
+    <t>Goldman Sachs Financial Conditions Index, M2 YoY</t>
+  </si>
+  <si>
+    <t>Consumer Spending &amp; Business Confidence</t>
+  </si>
+  <si>
+    <t>SMIDs are domestically oriented and sensitive to consumption/business cycles.</t>
+  </si>
+  <si>
+    <t>Retail Sales, PCE, NFIB Optimism Index</t>
+  </si>
+  <si>
+    <t>Inflation Expectations</t>
+  </si>
+  <si>
+    <t>Higher expected inflation leads to higher discount rates, hurting long-duration stocks.</t>
+  </si>
+  <si>
+    <t>5Y5Y Forward Inflation Expectation, Breakevens</t>
+  </si>
+  <si>
+    <t>Earnings Outlook &amp; Labor Productivity</t>
+  </si>
+  <si>
+    <t>Higher productivity supports margins and profitability in lean organizations.</t>
+  </si>
+  <si>
+    <t>Nonfarm Business Labor Productivity, Unit Labor Costs</t>
+  </si>
+  <si>
+    <t>Market Volatility &amp; Risk Sentiment</t>
+  </si>
+  <si>
+    <t>High volatility discourages risk-taking, impacting SMID and IPO stock performance.</t>
+  </si>
+  <si>
+    <t>VIX, Implied Correlation Index</t>
+  </si>
+  <si>
+    <t>Regulatory &amp; Tax Policy</t>
+  </si>
+  <si>
+    <t>Small firms are more exposed to policy changes due to lack of scale.</t>
+  </si>
+  <si>
+    <t>CBO tax revenue forecast, Congressional policy trackers</t>
+  </si>
+  <si>
+    <t>IPO Market Cycle / Equity Issuance Conditions</t>
+  </si>
+  <si>
+    <t>Favorable macro conditions enable more IPOs and better aftermarket performance.</t>
+  </si>
+  <si>
+    <t>Renaissance IPO Index, IPO Count &amp; Proceeds</t>
+  </si>
+  <si>
+    <t>Importance</t>
+  </si>
+  <si>
+    <t>Policy Type</t>
+  </si>
+  <si>
+    <t>Policy / Tool</t>
+  </si>
+  <si>
+    <t>Key Indicators / Sources</t>
+  </si>
+  <si>
+    <t>Monetary</t>
+  </si>
+  <si>
+    <t>Federal Funds Rate</t>
+  </si>
+  <si>
+    <t>Affects cost of capital and discount rate for growth-heavy firms.</t>
+  </si>
+  <si>
+    <t>FOMC Statements, Fed Dot Plot, FedWatch Tool</t>
+  </si>
+  <si>
+    <t>Quantitative Easing / Tightening</t>
+  </si>
+  <si>
+    <t>Changes system liquidity and investor risk appetite.</t>
+  </si>
+  <si>
+    <t>Fed Balance Sheet (H.4.1), SOMA Holdings, NY Fed</t>
+  </si>
+  <si>
+    <t>Forward Guidance</t>
+  </si>
+  <si>
+    <t>Shapes expectations of future policy, affecting discount rates.</t>
+  </si>
+  <si>
+    <t>FOMC Minutes, Fed Speeches, Treasury Futures Curve</t>
+  </si>
+  <si>
+    <t>Yield Curve Management</t>
+  </si>
+  <si>
+    <t>Yield curve shape affects recession probability and lending appetite.</t>
+  </si>
+  <si>
+    <t>10Y-2Y Spread, 3M-10Y Spread, NY Fed Recession Probabilities</t>
+  </si>
+  <si>
+    <t>Fiscal</t>
+  </si>
+  <si>
+    <t>Corporate Tax Policy</t>
+  </si>
+  <si>
+    <t>Directly affects after-tax earnings for small firms.</t>
+  </si>
+  <si>
+    <t>Congressional Budget Office (CBO), Treasury Tax Policy Proposals</t>
+  </si>
+  <si>
+    <t>Capital Gains &amp; IPO Taxation</t>
+  </si>
+  <si>
+    <t>Influences investor appetite and timing of IPO exits.</t>
+  </si>
+  <si>
+    <t>IRS Policy Memos, Congressional Hearings, White House Proposals</t>
+  </si>
+  <si>
+    <t>Small Business Subsidies / Stimulus</t>
+  </si>
+  <si>
+    <t>Provides liquidity relief and boosts demand for small businesses.</t>
+  </si>
+  <si>
+    <t>SBA Updates, PPP Data, Infrastructure Bill Disbursements</t>
+  </si>
+  <si>
+    <t>Government Spending Mix</t>
+  </si>
+  <si>
+    <t>Targeted capex boosts local and regional SMID demand.</t>
+  </si>
+  <si>
+    <t>OMB Budget Breakdown, Congressional Spending Bills</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Affects </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cost of capital</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; higher rates hurt growth-oriented firms with longer duration cash flows.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/graph/?g=1JBRt</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/graph/?g=1JBRx</t>
   </si>
 </sst>
 </file>
@@ -776,7 +986,14 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -787,6 +1004,32 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B5547A4E-3D2F-45D9-9371-F5A95BB3266A}" name="Table1" displayName="Table1" ref="A1:D10" totalsRowShown="0">
+  <autoFilter ref="A1:D10" xr:uid="{B5547A4E-3D2F-45D9-9371-F5A95BB3266A}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{A3EC4DBE-379C-4EB4-8ABE-DD0114A9058E}" name="Importance" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{F984C1C5-D364-4ABC-BD84-DE6D60A94B5E}" name="Factor"/>
+    <tableColumn id="3" xr3:uid="{32899D69-406B-477D-B9F5-79E1FBCFDD45}" name="Rationale"/>
+    <tableColumn id="4" xr3:uid="{5A583DCC-D16A-4170-A2AE-906CC63C1A2F}" name="Key Indicators"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4B75D266-516B-4648-85EA-E0C59701E7A0}" name="Table2" displayName="Table2" ref="A14:D22" totalsRowShown="0">
+  <autoFilter ref="A14:D22" xr:uid="{4B75D266-516B-4648-85EA-E0C59701E7A0}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{5F3690EE-9C07-4FA0-888F-B40106AA3B2B}" name="Policy Type" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{09C54442-3B23-4519-B6BA-6A20897D3560}" name="Policy / Tool"/>
+    <tableColumn id="3" xr3:uid="{8AD9DB09-2257-4B10-A8D3-1A7C092C9BEA}" name="Rationale"/>
+    <tableColumn id="4" xr3:uid="{50A36E15-DF15-4AA5-B7F7-CCB7EBE8448A}" name="Key Indicators / Sources"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1052,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
@@ -1083,22 +1326,22 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" t="s">
         <v>150</v>
-      </c>
-      <c r="G2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1106,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>0</v>
@@ -1118,7 +1361,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
         <v>4</v>
@@ -1129,7 +1372,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>8</v>
@@ -1152,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>12</v>
@@ -1164,10 +1407,10 @@
         <v>10</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1175,341 +1418,351 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>46</v>
+        <v>156</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>152</v>
+        <v>23</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>18</v>
+        <v>44</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
-      </c>
+      <c r="F7" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H7" s="11"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G8" t="s">
-        <v>45</v>
+        <v>14</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>153</v>
       </c>
       <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" t="s">
         <v>133</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F11" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G11" t="s">
         <v>134</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="H11" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F11" s="2"/>
-      <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>159</v>
-      </c>
+      <c r="F12" s="2"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" t="s">
-        <v>40</v>
+      <c r="A13" s="10" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>137</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>26</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>155</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
       <c r="D16" t="s">
         <v>6</v>
       </c>
       <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" t="s">
         <v>24</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
       <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" t="s">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
-        <v>138</v>
+      <c r="G18" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G20" t="s">
-        <v>142</v>
+      <c r="A20" s="10" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21" t="s">
+        <v>132</v>
+      </c>
+      <c r="E21" t="s">
+        <v>133</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G21" t="s">
         <v>141</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="D21" t="s">
-        <v>133</v>
-      </c>
-      <c r="E21" t="s">
-        <v>134</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C23" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="D23" t="s">
         <v>145</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E23" t="s">
         <v>146</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F23" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G23" t="s">
         <v>147</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G22" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F14" r:id="rId1" display="https://www.newyorkfed.org/microeconomics/hhdc/background.html" xr:uid="{7ABD0E68-817E-402B-ACF8-FE4D56554007}"/>
-    <hyperlink ref="F13" r:id="rId2" display="https://tradingeconomics.com/united-states/consumer-confidence" xr:uid="{CDD22088-A0F9-47C3-A2CC-99ED863C1E26}"/>
+    <hyperlink ref="F15" r:id="rId1" display="https://www.newyorkfed.org/microeconomics/hhdc/background.html" xr:uid="{7ABD0E68-817E-402B-ACF8-FE4D56554007}"/>
+    <hyperlink ref="F14" r:id="rId2" display="https://tradingeconomics.com/united-states/consumer-confidence" xr:uid="{CDD22088-A0F9-47C3-A2CC-99ED863C1E26}"/>
     <hyperlink ref="F3" r:id="rId3" xr:uid="{5270A901-1899-4307-B0B0-C72E9E77F624}"/>
     <hyperlink ref="F4" r:id="rId4" xr:uid="{ADFAF753-8B08-4D84-98B2-8CAE04FE9EC9}"/>
-    <hyperlink ref="F8" r:id="rId5" xr:uid="{15FDA271-E860-41C1-9B24-21D3F0C43CD4}"/>
-    <hyperlink ref="F7" r:id="rId6" xr:uid="{6D483326-997D-48FE-B8C6-D4F1B83BCF7D}"/>
-    <hyperlink ref="F9" r:id="rId7" xr:uid="{1FB277DF-1E4E-4FD2-8683-23994E3B9066}"/>
-    <hyperlink ref="F2" r:id="rId8" xr:uid="{C0550891-D622-4BB5-8D02-DAFB59113398}"/>
-    <hyperlink ref="F5" r:id="rId9" xr:uid="{B07DC080-5E9F-4E06-866C-AAB2C1C66EDB}"/>
-    <hyperlink ref="F6" r:id="rId10" xr:uid="{6497ACBE-E7E4-45ED-A69B-360853D7CA1F}"/>
-    <hyperlink ref="H10" r:id="rId11" display="https://www.cboe.com/us/indices/implied/" xr:uid="{DB898EC2-8D45-4E3B-ABB4-49784040313A}"/>
-    <hyperlink ref="F10" r:id="rId12" xr:uid="{0E8BC757-721A-4976-B2E7-D3D27CB055FA}"/>
-    <hyperlink ref="F20" r:id="rId13" xr:uid="{69772D0B-E80B-4D37-9B2C-D2CDCCE0E78D}"/>
-    <hyperlink ref="F21" r:id="rId14" xr:uid="{519892C7-B0C2-4847-AD92-17AC10D871A4}"/>
-    <hyperlink ref="F22" r:id="rId15" xr:uid="{A07C074D-2405-492D-9E3E-E5412C8A3032}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{6D483326-997D-48FE-B8C6-D4F1B83BCF7D}"/>
+    <hyperlink ref="F10" r:id="rId6" xr:uid="{1FB277DF-1E4E-4FD2-8683-23994E3B9066}"/>
+    <hyperlink ref="F2" r:id="rId7" xr:uid="{C0550891-D622-4BB5-8D02-DAFB59113398}"/>
+    <hyperlink ref="F8" r:id="rId8" xr:uid="{6497ACBE-E7E4-45ED-A69B-360853D7CA1F}"/>
+    <hyperlink ref="H11" r:id="rId9" display="https://www.cboe.com/us/indices/implied/" xr:uid="{DB898EC2-8D45-4E3B-ABB4-49784040313A}"/>
+    <hyperlink ref="F11" r:id="rId10" xr:uid="{0E8BC757-721A-4976-B2E7-D3D27CB055FA}"/>
+    <hyperlink ref="F21" r:id="rId11" xr:uid="{69772D0B-E80B-4D37-9B2C-D2CDCCE0E78D}"/>
+    <hyperlink ref="F22" r:id="rId12" xr:uid="{519892C7-B0C2-4847-AD92-17AC10D871A4}"/>
+    <hyperlink ref="F23" r:id="rId13" xr:uid="{A07C074D-2405-492D-9E3E-E5412C8A3032}"/>
+    <hyperlink ref="H6" r:id="rId14" xr:uid="{15FDA271-E860-41C1-9B24-21D3F0C43CD4}"/>
+    <hyperlink ref="F6" r:id="rId15" xr:uid="{7C51A9C8-EF3F-4990-9683-F7DAB0CFD20D}"/>
+    <hyperlink ref="F7" r:id="rId16" xr:uid="{12597AE8-7E71-49BC-A7C7-1DABE4AAC718}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId16"/>
-  <legacyDrawing r:id="rId17"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId17"/>
+  <legacyDrawing r:id="rId18"/>
 </worksheet>
 </file>
 
@@ -1528,416 +1781,416 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s">
         <v>47</v>
       </c>
-      <c r="C1" t="s">
-        <v>48</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C2">
         <v>336110</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3">
         <v>441110</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>441120</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>4231</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>441330</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7">
         <v>524126</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>522220</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D10" s="9"/>
       <c r="G10" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>118</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G11" s="7">
         <v>4</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G14" s="7">
         <v>4</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I14" s="7"/>
       <c r="N14" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G15" s="7">
         <v>4</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G18">
         <v>6</v>
       </c>
       <c r="H18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G19">
         <v>6</v>
       </c>
       <c r="H19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G21">
         <v>4</v>
       </c>
       <c r="H21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G24" s="7">
         <v>5</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I24" s="7"/>
       <c r="N24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G25">
         <v>6</v>
       </c>
       <c r="H25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G26">
         <v>6</v>
       </c>
       <c r="H26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G27">
         <v>6</v>
       </c>
       <c r="H27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G28" s="7">
         <v>5</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G29">
         <v>5</v>
       </c>
       <c r="H29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G30">
         <v>6</v>
       </c>
       <c r="H30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G31">
         <v>6</v>
       </c>
       <c r="H31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -1945,7 +2198,7 @@
         <v>7</v>
       </c>
       <c r="H32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="7:8" x14ac:dyDescent="0.3">
@@ -1953,7 +2206,7 @@
         <v>5</v>
       </c>
       <c r="H33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="7:8" x14ac:dyDescent="0.3">
@@ -1961,7 +2214,7 @@
         <v>6</v>
       </c>
       <c r="H34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="7:8" x14ac:dyDescent="0.3">
@@ -1969,7 +2222,7 @@
         <v>6</v>
       </c>
       <c r="H35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="7:8" x14ac:dyDescent="0.3">
@@ -1977,7 +2230,7 @@
         <v>7</v>
       </c>
       <c r="H36" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="7:8" x14ac:dyDescent="0.3">
@@ -1985,7 +2238,7 @@
         <v>6</v>
       </c>
       <c r="H37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="7:8" x14ac:dyDescent="0.3">
@@ -1993,7 +2246,7 @@
         <v>7</v>
       </c>
       <c r="H38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2008,4 +2261,290 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA9074B-733D-450E-898F-9664AA9E6DC2}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="79.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D14" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" t="s">
+        <v>195</v>
+      </c>
+      <c r="D15" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B16" t="s">
+        <v>197</v>
+      </c>
+      <c r="C16" t="s">
+        <v>198</v>
+      </c>
+      <c r="D16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" t="s">
+        <v>200</v>
+      </c>
+      <c r="C17" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C19" t="s">
+        <v>208</v>
+      </c>
+      <c r="D19" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" t="s">
+        <v>210</v>
+      </c>
+      <c r="C20" t="s">
+        <v>211</v>
+      </c>
+      <c r="D20" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C21" t="s">
+        <v>214</v>
+      </c>
+      <c r="D21" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B22" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22" t="s">
+        <v>217</v>
+      </c>
+      <c r="D22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>